--- a/case_studies/high_feedstock_availability_10_dd/2050/technologies.xlsx
+++ b/case_studies/high_feedstock_availability_10_dd/2050/technologies.xlsx
@@ -694,10 +694,10 @@
         <v>115.62</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>481.05</v>
+        <v>481.02</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>85.56</v>
+        <v>85.06</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>57.64</v>
@@ -718,7 +718,7 @@
         <v>501.68</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>32.72</v>
+        <v>32.7</v>
       </c>
       <c r="S2" s="3" t="n">
         <v>42.53</v>
@@ -733,7 +733,7 @@
         <v>186.96</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>267.26</v>
+        <v>267.23</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>11.99</v>
@@ -867,7 +867,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>39.95</v>
@@ -888,37 +888,37 @@
         <v>487.9</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>947.59</v>
+        <v>943.29</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>73.03</v>
+        <v>73.38</v>
       </c>
       <c r="M4" s="3" t="n">
+        <v>547.39</v>
+      </c>
+      <c r="N4" s="3" t="n">
         <v>1369.36</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>601.88</v>
-      </c>
       <c r="O4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>1360.23</v>
+        <v>1360.89</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>1473.19</v>
+        <v>1473.84</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>296.67</v>
+        <v>296.57</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>86.64</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>560.9299999999999</v>
+        <v>561.28</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
         <v>54.5</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>281.85</v>
+        <v>281.74</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>23.97</v>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>36.87</v>
+        <v>36</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>216.89</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>38.39</v>
@@ -985,13 +985,13 @@
         <v>108.65</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>505.08</v>
+        <v>505.05</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>166.23</v>
+        <v>166.16</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>745.4</v>
@@ -1003,10 +1003,10 @@
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>128.41</v>
+        <v>128.15</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>171.24</v>
+        <v>170.99</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
@@ -1024,13 +1024,13 @@
         <v>2.74</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>512.3200000000001</v>
+        <v>523.46</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>23.97</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>28202.14</v>
+        <v>29282.39</v>
       </c>
       <c r="Z5" s="5" t="n">
         <v>204.22</v>
@@ -1061,7 +1061,7 @@
         <v>89.48999999999999</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>315.28</v>
+        <v>367.42</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>62.79</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>12.02</v>
+        <v>0.8</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.11</v>
@@ -1082,37 +1082,37 @@
         <v>67.03</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>163.14</v>
+        <v>173.36</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>42.99</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>162.27</v>
+        <v>121.06</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>174.71</v>
+        <v>565.33</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>174.71</v>
+        <v>331.39</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>531.3</v>
+        <v>447.81</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>551.1900000000001</v>
+        <v>455.76</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>67.84</v>
+        <v>73.12</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>13.53</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>229.3</v>
+        <v>188.09</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>0</v>
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>67.84</v>
+        <v>73.12</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>23.97</v>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -1279,10 +1279,10 @@
         <v>278.28</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>99.58</v>
+        <v>49.72</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>148.29</v>
+        <v>147.5</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>136.33</v>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>447.37</v>
+        <v>445.68</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>519.23</v>
+        <v>527.97</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>174.64</v>
@@ -1306,7 +1306,7 @@
         <v>106.83</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>214.41</v>
+        <v>213.62</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
@@ -1315,13 +1315,13 @@
         <v>8.67</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>298</v>
+        <v>442.56</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>23.97</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>19670.76</v>
+        <v>33149.53</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>0</v>
